--- a/salidas/empresas/TRV.xlsx
+++ b/salidas/empresas/TRV.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>28.01417922973633</v>
+        <v>28.01418304443359</v>
       </c>
       <c r="C2" t="n">
         <v>45.38000106811523</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>26.5325813293457</v>
+        <v>26.53258323669434</v>
       </c>
       <c r="C3" t="n">
         <v>42.97999954223633</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>25.93792915344238</v>
+        <v>25.93791007995605</v>
       </c>
       <c r="C4" t="n">
         <v>41.79000091552734</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>27.32823181152344</v>
+        <v>27.32822418212891</v>
       </c>
       <c r="C5" t="n">
         <v>44.02999877929688</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>27.32201766967773</v>
+        <v>27.32203483581543</v>
       </c>
       <c r="C6" t="n">
         <v>44.02000045776367</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>27.83899307250977</v>
+        <v>27.83898162841797</v>
       </c>
       <c r="C7" t="n">
         <v>44.58000183105469</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>28.60084915161133</v>
+        <v>28.60084533691406</v>
       </c>
       <c r="C8" t="n">
         <v>45.79999923706055</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>27.41435813903809</v>
+        <v>27.41435050964355</v>
       </c>
       <c r="C9" t="n">
         <v>43.90000152587891</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>29.45396423339844</v>
+        <v>29.45395469665527</v>
       </c>
       <c r="C10" t="n">
         <v>46.88999938964844</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>32.11731338500977</v>
+        <v>32.11731719970703</v>
       </c>
       <c r="C11" t="n">
         <v>51.13000106811523</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>32.54446411132812</v>
+        <v>32.54446029663086</v>
       </c>
       <c r="C12" t="n">
         <v>51.81000137329102</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>33.89518356323242</v>
+        <v>33.89519500732422</v>
       </c>
       <c r="C13" t="n">
         <v>53.68999862670898</v>
@@ -710,7 +722,7 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>32.03912353515625</v>
+        <v>32.03910827636719</v>
       </c>
       <c r="C15" t="n">
         <v>50.75</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>32.84822463989258</v>
+        <v>32.84823226928711</v>
       </c>
       <c r="C16" t="n">
         <v>51.77000045776367</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>34.32662582397461</v>
+        <v>34.32662963867188</v>
       </c>
       <c r="C17" t="n">
         <v>54.09999847412109</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>34.37103271484375</v>
+        <v>34.37104034423828</v>
       </c>
       <c r="C18" t="n">
         <v>54.16999816894531</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>34.12601089477539</v>
+        <v>34.12601852416992</v>
       </c>
       <c r="C19" t="n">
         <v>53.5</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>32.39102935791016</v>
+        <v>32.39100646972656</v>
       </c>
       <c r="C20" t="n">
         <v>50.77999877929688</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>32.23794174194336</v>
+        <v>32.23791885375977</v>
       </c>
       <c r="C21" t="n">
         <v>50.54000091552734</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>32.29549407958984</v>
+        <v>32.29548645019531</v>
       </c>
       <c r="C22" t="n">
         <v>50.34000015258789</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>33.49517440795898</v>
+        <v>33.49516677856445</v>
       </c>
       <c r="C23" t="n">
         <v>52.20999908447266</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>34.07257080078125</v>
+        <v>34.07256698608398</v>
       </c>
       <c r="C24" t="n">
         <v>53.11000061035156</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>34.70101165771484</v>
+        <v>34.70099258422852</v>
       </c>
       <c r="C25" t="n">
         <v>53.79999923706055</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>31.02449035644531</v>
+        <v>31.02449798583984</v>
       </c>
       <c r="C26" t="n">
         <v>48.09999847412109</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>29.93445777893066</v>
+        <v>29.93445205688477</v>
       </c>
       <c r="C27" t="n">
         <v>46.40999984741211</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>31.05287170410156</v>
+        <v>31.05286598205566</v>
       </c>
       <c r="C28" t="n">
         <v>47.84999847412109</v>
@@ -995,7 +1007,7 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
@@ -1014,7 +1026,7 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>28.33418273925781</v>
+        <v>28.33419036865234</v>
       </c>
       <c r="C31" t="n">
         <v>43.40000152587891</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>28.80425071716309</v>
+        <v>28.80424308776855</v>
       </c>
       <c r="C32" t="n">
         <v>44.11999893188477</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>28.83036804199219</v>
+        <v>28.83035850524902</v>
       </c>
       <c r="C33" t="n">
         <v>44.15999984741211</v>
@@ -1090,7 +1102,7 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
@@ -1109,7 +1121,7 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>28.69632339477539</v>
+        <v>28.69631958007812</v>
       </c>
       <c r="C36" t="n">
         <v>43.65000152587891</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>29.92210006713867</v>
+        <v>29.9221019744873</v>
       </c>
       <c r="C37" t="n">
         <v>45.20000076293945</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>25.57941818237305</v>
+        <v>25.57942581176758</v>
       </c>
       <c r="C38" t="n">
         <v>38.63999938964844</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>23.93106651306152</v>
+        <v>23.93106079101562</v>
       </c>
       <c r="C39" t="n">
         <v>36.15000152587891</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>27.14333724975586</v>
+        <v>27.14333915710449</v>
       </c>
       <c r="C40" t="n">
         <v>40.63999938964844</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>27.47728538513184</v>
+        <v>27.47729110717773</v>
       </c>
       <c r="C41" t="n">
         <v>41.13999938964844</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>27.15670013427734</v>
+        <v>27.15669441223145</v>
       </c>
       <c r="C42" t="n">
         <v>40.65999984741211</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>27.59976005554199</v>
+        <v>27.59975051879883</v>
       </c>
       <c r="C43" t="n">
         <v>41.04000091552734</v>
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>28.96494674682617</v>
+        <v>28.96494293212891</v>
       </c>
       <c r="C44" t="n">
         <v>43.06999969482422</v>
@@ -1299,11 +1311,11 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>33.90789031982422</v>
+        <v>33.90787124633789</v>
       </c>
       <c r="C45" t="n">
         <v>50.41999816894531</v>
@@ -1324,11 +1336,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>33.30695343017578</v>
+        <v>33.30697250366211</v>
       </c>
       <c r="C46" t="n">
         <v>49.22999954223633</v>
@@ -1349,7 +1361,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
@@ -1374,11 +1386,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>35.44488906860352</v>
+        <v>35.44487762451172</v>
       </c>
       <c r="C48" t="n">
         <v>52.38999938964844</v>
@@ -1399,11 +1411,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>33.95477294921875</v>
+        <v>33.95478057861328</v>
       </c>
       <c r="C49" t="n">
         <v>49.86000061035156</v>
@@ -1424,11 +1436,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>34.50637817382812</v>
+        <v>34.50638198852539</v>
       </c>
       <c r="C50" t="n">
         <v>50.66999816894531</v>
@@ -1449,11 +1461,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>35.81390380859375</v>
+        <v>35.81390762329102</v>
       </c>
       <c r="C51" t="n">
         <v>52.59000015258789</v>
@@ -1474,11 +1486,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>36.95937728881836</v>
+        <v>36.95937347412109</v>
       </c>
       <c r="C52" t="n">
         <v>53.93999862670898</v>
@@ -1499,11 +1511,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>34.76674652099609</v>
+        <v>34.76675796508789</v>
       </c>
       <c r="C53" t="n">
         <v>50.7400016784668</v>
@@ -1524,11 +1536,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>33.89655685424805</v>
+        <v>33.89656066894531</v>
       </c>
       <c r="C54" t="n">
         <v>49.47000122070312</v>
@@ -1549,11 +1561,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>33.9993782043457</v>
+        <v>33.99937057495117</v>
       </c>
       <c r="C55" t="n">
         <v>49.25</v>
@@ -1574,11 +1586,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>34.82779693603516</v>
+        <v>34.82778549194336</v>
       </c>
       <c r="C56" t="n">
         <v>50.45000076293945</v>
@@ -1599,7 +1611,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
@@ -1624,7 +1636,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
@@ -1649,11 +1661,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>38.38254547119141</v>
+        <v>38.38254928588867</v>
       </c>
       <c r="C59" t="n">
         <v>55.20000076293945</v>
@@ -1674,11 +1686,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>37.54119873046875</v>
+        <v>37.54120254516602</v>
       </c>
       <c r="C60" t="n">
         <v>53.9900016784668</v>
@@ -1699,11 +1711,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>38.9931526184082</v>
+        <v>38.99314117431641</v>
       </c>
       <c r="C61" t="n">
         <v>55.70999908447266</v>
@@ -1724,11 +1736,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>39.37810516357422</v>
+        <v>39.37811279296875</v>
       </c>
       <c r="C62" t="n">
         <v>56.2599983215332</v>
@@ -1749,7 +1761,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
@@ -1774,11 +1786,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>41.88764953613281</v>
+        <v>41.88763427734375</v>
       </c>
       <c r="C64" t="n">
         <v>59.47999954223633</v>
@@ -1799,11 +1811,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>44.56371688842773</v>
+        <v>44.56371307373047</v>
       </c>
       <c r="C65" t="n">
         <v>63.27999877929688</v>
@@ -1824,11 +1836,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>43.71865463256836</v>
+        <v>43.71864700317383</v>
       </c>
       <c r="C66" t="n">
         <v>62.08000183105469</v>
@@ -1849,7 +1861,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
@@ -1874,11 +1886,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>39.08596801757812</v>
+        <v>39.08597183227539</v>
       </c>
       <c r="C68" t="n">
         <v>55.13000106811523</v>
@@ -1899,11 +1911,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>35.77504348754883</v>
+        <v>35.7750244140625</v>
       </c>
       <c r="C69" t="n">
         <v>50.45999908447266</v>
@@ -1924,11 +1936,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>34.84287261962891</v>
+        <v>34.8428840637207</v>
       </c>
       <c r="C70" t="n">
         <v>48.72999954223633</v>
@@ -1949,7 +1961,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
@@ -1974,11 +1986,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>40.21982192993164</v>
+        <v>40.21981048583984</v>
       </c>
       <c r="C72" t="n">
         <v>56.25</v>
@@ -1999,11 +2011,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>42.62339782714844</v>
+        <v>42.62339019775391</v>
       </c>
       <c r="C73" t="n">
         <v>59.16999816894531</v>
@@ -2024,11 +2036,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>41.99670028686523</v>
+        <v>41.99668884277344</v>
       </c>
       <c r="C74" t="n">
         <v>58.29999923706055</v>
@@ -2049,11 +2061,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>41.75897598266602</v>
+        <v>41.75896835327148</v>
       </c>
       <c r="C75" t="n">
         <v>57.97000122070312</v>
@@ -2078,11 +2090,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>42.95403289794922</v>
+        <v>42.95402908325195</v>
       </c>
       <c r="C76" t="n">
         <v>59.20000076293945</v>
@@ -2107,11 +2119,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>46.66897201538086</v>
+        <v>46.66896820068359</v>
       </c>
       <c r="C77" t="n">
         <v>64.31999969482422</v>
@@ -2136,7 +2148,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
@@ -2165,11 +2177,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>46.67382431030273</v>
+        <v>46.67381286621094</v>
       </c>
       <c r="C79" t="n">
         <v>63.84000015258789</v>
@@ -2194,7 +2206,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
@@ -2223,11 +2235,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>47.33181381225586</v>
+        <v>47.3317985534668</v>
       </c>
       <c r="C81" t="n">
         <v>64.73999786376953</v>
@@ -2252,11 +2264,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>50.26360702514648</v>
+        <v>50.26361846923828</v>
       </c>
       <c r="C82" t="n">
         <v>68.26000213623047</v>
@@ -2281,11 +2293,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>52.23705291748047</v>
+        <v>52.23704147338867</v>
       </c>
       <c r="C83" t="n">
         <v>70.94000244140625</v>
@@ -2310,11 +2322,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>52.14867401123047</v>
+        <v>52.14866638183594</v>
       </c>
       <c r="C84" t="n">
         <v>70.81999969482422</v>
@@ -2339,11 +2351,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>53.21583938598633</v>
+        <v>53.21582794189453</v>
       </c>
       <c r="C85" t="n">
         <v>71.81999969482422</v>
@@ -2368,11 +2380,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>58.13580322265625</v>
+        <v>58.13579940795898</v>
       </c>
       <c r="C86" t="n">
         <v>78.45999908447266</v>
@@ -2397,11 +2409,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>59.58811187744141</v>
+        <v>59.58810043334961</v>
       </c>
       <c r="C87" t="n">
         <v>80.41999816894531</v>
@@ -2426,7 +2438,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
@@ -2455,11 +2467,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>63.64489364624023</v>
+        <v>63.64491271972656</v>
       </c>
       <c r="C89" t="n">
         <v>85.41000366210938</v>
@@ -2484,11 +2496,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>62.38559341430664</v>
+        <v>62.38554763793945</v>
       </c>
       <c r="C90" t="n">
         <v>83.72000122070312</v>
@@ -2513,11 +2525,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>59.91819381713867</v>
+        <v>59.9182014465332</v>
       </c>
       <c r="C91" t="n">
         <v>79.91999816894531</v>
@@ -2542,11 +2554,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>62.63973236083984</v>
+        <v>62.63972473144531</v>
       </c>
       <c r="C92" t="n">
         <v>83.55000305175781</v>
@@ -2571,11 +2583,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>59.90322113037109</v>
+        <v>59.9031982421875</v>
       </c>
       <c r="C93" t="n">
         <v>79.90000152587891</v>
@@ -2600,11 +2612,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>63.95080947875977</v>
+        <v>63.9508171081543</v>
       </c>
       <c r="C94" t="n">
         <v>84.76999664306641</v>
@@ -2629,7 +2641,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
@@ -2658,11 +2670,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>68.45459747314453</v>
+        <v>68.45461273193359</v>
       </c>
       <c r="C96" t="n">
         <v>90.73999786376953</v>
@@ -2687,11 +2699,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>68.69437408447266</v>
+        <v>68.69440460205078</v>
       </c>
       <c r="C97" t="n">
         <v>90.54000091552734</v>
@@ -2716,11 +2728,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>61.66867446899414</v>
+        <v>61.66865158081055</v>
       </c>
       <c r="C98" t="n">
         <v>81.27999877929688</v>
@@ -2745,11 +2757,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>63.61096954345703</v>
+        <v>63.6109733581543</v>
       </c>
       <c r="C99" t="n">
         <v>83.83999633789062</v>
@@ -2774,11 +2786,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>64.951904296875</v>
+        <v>64.95188903808594</v>
       </c>
       <c r="C100" t="n">
         <v>85.09999847412109</v>
@@ -2803,11 +2815,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>69.13445281982422</v>
+        <v>69.13443756103516</v>
       </c>
       <c r="C101" t="n">
         <v>90.58000183105469</v>
@@ -2832,11 +2844,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>71.32494354248047</v>
+        <v>71.32496643066406</v>
       </c>
       <c r="C102" t="n">
         <v>93.44999694824219</v>
@@ -2861,11 +2873,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>72.21637725830078</v>
+        <v>72.21638488769531</v>
       </c>
       <c r="C103" t="n">
         <v>94.06999969482422</v>
@@ -2890,11 +2902,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>68.75411224365234</v>
+        <v>68.75410461425781</v>
       </c>
       <c r="C104" t="n">
         <v>89.55999755859375</v>
@@ -2919,11 +2931,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>72.70768737792969</v>
+        <v>72.70769500732422</v>
       </c>
       <c r="C105" t="n">
         <v>94.70999908447266</v>
@@ -2948,11 +2960,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>72.54007720947266</v>
+        <v>72.54009246826172</v>
       </c>
       <c r="C106" t="n">
         <v>93.94000244140625</v>
@@ -2977,11 +2989,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>77.83734893798828</v>
+        <v>77.83732604980469</v>
       </c>
       <c r="C107" t="n">
         <v>100.8000030517578</v>
@@ -3006,7 +3018,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
@@ -3035,7 +3047,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
@@ -3064,11 +3076,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>79.814453125</v>
+        <v>79.81447601318359</v>
       </c>
       <c r="C110" t="n">
         <v>102.8199996948242</v>
@@ -3093,11 +3105,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>83.40074920654297</v>
+        <v>83.4007568359375</v>
       </c>
       <c r="C111" t="n">
         <v>107.4400024414062</v>
@@ -3122,11 +3134,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>84.36763000488281</v>
+        <v>84.36759948730469</v>
       </c>
       <c r="C112" t="n">
         <v>108.129997253418</v>
@@ -3151,7 +3163,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
@@ -3180,11 +3192,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>78.89812469482422</v>
+        <v>78.89813232421875</v>
       </c>
       <c r="C114" t="n">
         <v>101.120002746582</v>
@@ -3209,7 +3221,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
@@ -3238,11 +3250,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>83.31104278564453</v>
+        <v>83.31108093261719</v>
       </c>
       <c r="C116" t="n">
         <v>106.120002746582</v>
@@ -3267,11 +3279,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>78.15317535400391</v>
+        <v>78.15320587158203</v>
       </c>
       <c r="C117" t="n">
         <v>99.55000305175781</v>
@@ -3296,11 +3308,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>78.62810516357422</v>
+        <v>78.62808227539062</v>
       </c>
       <c r="C118" t="n">
         <v>99.52999877929688</v>
@@ -3325,11 +3337,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>89.18241882324219</v>
+        <v>89.18242645263672</v>
       </c>
       <c r="C119" t="n">
         <v>112.8899993896484</v>
@@ -3354,11 +3366,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>90.50961303710938</v>
+        <v>90.50960540771484</v>
       </c>
       <c r="C120" t="n">
         <v>114.5699996948242</v>
@@ -3383,11 +3395,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>89.64013671875</v>
+        <v>89.64008331298828</v>
       </c>
       <c r="C121" t="n">
         <v>112.8600006103516</v>
@@ -3412,11 +3424,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>85.01750183105469</v>
+        <v>85.01752471923828</v>
       </c>
       <c r="C122" t="n">
         <v>107.0400009155273</v>
@@ -3441,11 +3453,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>85.39877319335938</v>
+        <v>85.39876556396484</v>
       </c>
       <c r="C123" t="n">
         <v>107.5199966430664</v>
@@ -3470,7 +3482,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
@@ -3499,11 +3511,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>87.77404022216797</v>
+        <v>87.77403259277344</v>
       </c>
       <c r="C125" t="n">
         <v>109.9000015258789</v>
@@ -3528,11 +3540,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>91.16038513183594</v>
+        <v>91.16039276123047</v>
       </c>
       <c r="C126" t="n">
         <v>114.1399993896484</v>
@@ -3557,11 +3569,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>95.63313293457031</v>
+        <v>95.63310241699219</v>
       </c>
       <c r="C127" t="n">
         <v>119.0400009155273</v>
@@ -3586,11 +3598,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>93.36760711669922</v>
+        <v>93.36763000488281</v>
       </c>
       <c r="C128" t="n">
         <v>116.2200012207031</v>
@@ -3615,11 +3627,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>95.36799621582031</v>
+        <v>95.36798858642578</v>
       </c>
       <c r="C129" t="n">
         <v>118.7099990844727</v>
@@ -3644,11 +3656,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>92.5457763671875</v>
+        <v>92.54576110839844</v>
       </c>
       <c r="C130" t="n">
         <v>114.5500030517578</v>
@@ -3673,11 +3685,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>87.39939117431641</v>
+        <v>87.39940643310547</v>
       </c>
       <c r="C131" t="n">
         <v>108.1800003051758</v>
@@ -3702,11 +3714,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>91.57628631591797</v>
+        <v>91.57627105712891</v>
       </c>
       <c r="C132" t="n">
         <v>113.3499984741211</v>
@@ -3731,11 +3743,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>99.4744873046875</v>
+        <v>99.47446441650391</v>
       </c>
       <c r="C133" t="n">
         <v>122.4199981689453</v>
@@ -3760,7 +3772,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
@@ -3789,11 +3801,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>99.32819366455078</v>
+        <v>99.32820892333984</v>
       </c>
       <c r="C135" t="n">
         <v>122.2399978637695</v>
@@ -3818,11 +3830,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>98.48711395263672</v>
+        <v>98.48709106445312</v>
       </c>
       <c r="C136" t="n">
         <v>120.5400009155273</v>
@@ -3847,11 +3859,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>99.40218353271484</v>
+        <v>99.40219879150391</v>
       </c>
       <c r="C137" t="n">
         <v>121.6600036621094</v>
@@ -3876,11 +3888,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>102.0085983276367</v>
+        <v>102.0085830688477</v>
       </c>
       <c r="C138" t="n">
         <v>124.8499984741211</v>
@@ -3905,11 +3917,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>103.9848556518555</v>
+        <v>103.9848403930664</v>
       </c>
       <c r="C139" t="n">
         <v>126.5299987792969</v>
@@ -3934,7 +3946,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
@@ -3963,11 +3975,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>99.58814239501953</v>
+        <v>99.588134765625</v>
       </c>
       <c r="C141" t="n">
         <v>121.1800003051758</v>
@@ -3992,11 +4004,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>101.3089294433594</v>
+        <v>101.3089447021484</v>
       </c>
       <c r="C142" t="n">
         <v>122.5199966430664</v>
@@ -4021,11 +4033,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>109.5198135375977</v>
+        <v>109.5197982788086</v>
       </c>
       <c r="C143" t="n">
         <v>132.4499969482422</v>
@@ -4050,11 +4062,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>112.0996932983398</v>
+        <v>112.0996704101562</v>
       </c>
       <c r="C144" t="n">
         <v>135.5700073242188</v>
@@ -4079,11 +4091,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>112.7625122070312</v>
+        <v>112.7625045776367</v>
       </c>
       <c r="C145" t="n">
         <v>135.6399993896484</v>
@@ -4108,11 +4120,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>124.6339874267578</v>
+        <v>124.634033203125</v>
       </c>
       <c r="C146" t="n">
         <v>149.9199981689453</v>
@@ -4137,11 +4149,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>115.5557632446289</v>
+        <v>115.555778503418</v>
       </c>
       <c r="C147" t="n">
         <v>139</v>
@@ -4166,11 +4178,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>116.0409927368164</v>
+        <v>116.0410003662109</v>
       </c>
       <c r="C148" t="n">
         <v>138.8600006103516</v>
@@ -4195,7 +4207,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
@@ -4224,7 +4236,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
@@ -4253,11 +4265,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>102.8507308959961</v>
+        <v>102.8507385253906</v>
       </c>
       <c r="C151" t="n">
         <v>122.3399963378906</v>
@@ -4282,11 +4294,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>109.408203125</v>
+        <v>109.4081954956055</v>
       </c>
       <c r="C152" t="n">
         <v>130.1399993896484</v>
@@ -4311,11 +4323,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>110.6356048583984</v>
+        <v>110.6355972290039</v>
       </c>
       <c r="C153" t="n">
         <v>131.6000061035156</v>
@@ -4340,11 +4352,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>109.6837692260742</v>
+        <v>109.6837539672852</v>
       </c>
       <c r="C154" t="n">
         <v>129.7100067138672</v>
@@ -4369,11 +4381,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>105.8108825683594</v>
+        <v>105.8108673095703</v>
       </c>
       <c r="C155" t="n">
         <v>125.129997253418</v>
@@ -4398,11 +4410,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>110.2418518066406</v>
+        <v>110.2418594360352</v>
       </c>
       <c r="C156" t="n">
         <v>130.3699951171875</v>
@@ -4427,7 +4439,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
@@ -4456,7 +4468,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
@@ -4485,11 +4497,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>113.0840377807617</v>
+        <v>113.0840225219727</v>
       </c>
       <c r="C159" t="n">
         <v>132.9100036621094</v>
@@ -4514,7 +4526,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
@@ -4543,11 +4555,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>123.0274658203125</v>
+        <v>123.0274887084961</v>
       </c>
       <c r="C161" t="n">
         <v>143.75</v>
@@ -4572,11 +4584,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>124.5851364135742</v>
+        <v>124.5851440429688</v>
       </c>
       <c r="C162" t="n">
         <v>145.5700073242188</v>
@@ -4601,11 +4613,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>128.673828125</v>
+        <v>128.6738739013672</v>
       </c>
       <c r="C163" t="n">
         <v>149.5200042724609</v>
@@ -4630,11 +4642,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>126.1781158447266</v>
+        <v>126.1781845092773</v>
       </c>
       <c r="C164" t="n">
         <v>146.6199951171875</v>
@@ -4659,11 +4671,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>126.4707489013672</v>
+        <v>126.4707717895508</v>
       </c>
       <c r="C165" t="n">
         <v>146.9600067138672</v>
@@ -4688,11 +4700,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>128.6497650146484</v>
+        <v>128.6497802734375</v>
       </c>
       <c r="C166" t="n">
         <v>148.6900024414062</v>
@@ -4717,11 +4729,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>113.3959197998047</v>
+        <v>113.3959274291992</v>
       </c>
       <c r="C167" t="n">
         <v>131.0599975585938</v>
@@ -4746,7 +4758,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
@@ -4775,11 +4787,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>119.2123565673828</v>
+        <v>119.2123641967773</v>
       </c>
       <c r="C169" t="n">
         <v>136.9499969482422</v>
@@ -4804,11 +4816,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>114.5726623535156</v>
+        <v>114.5726776123047</v>
       </c>
       <c r="C170" t="n">
         <v>131.6199951171875</v>
@@ -4833,7 +4845,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
@@ -4862,7 +4874,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
@@ -4891,7 +4903,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
@@ -4920,11 +4932,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>93.73975372314453</v>
+        <v>93.73974609375</v>
       </c>
       <c r="C174" t="n">
         <v>106.9800033569336</v>
@@ -4949,7 +4961,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
@@ -4978,11 +4990,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>100.9292068481445</v>
+        <v>100.9291839599609</v>
       </c>
       <c r="C176" t="n">
         <v>114.4199981689453</v>
@@ -5007,11 +5019,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>102.3581619262695</v>
+        <v>102.3581695556641</v>
       </c>
       <c r="C177" t="n">
         <v>116.0400009155273</v>
@@ -5036,11 +5048,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>96.15231323242188</v>
+        <v>96.15229797363281</v>
       </c>
       <c r="C178" t="n">
         <v>108.1900024414062</v>
@@ -5065,11 +5077,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>107.2792587280273</v>
+        <v>107.2792739868164</v>
       </c>
       <c r="C179" t="n">
         <v>120.7099990844727</v>
@@ -5094,11 +5106,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>115.2245559692383</v>
+        <v>115.2245712280273</v>
       </c>
       <c r="C180" t="n">
         <v>129.6499938964844</v>
@@ -5123,11 +5135,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>125.5406875610352</v>
+        <v>125.5407180786133</v>
       </c>
       <c r="C181" t="n">
         <v>140.3699951171875</v>
@@ -5152,11 +5164,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>121.9006805419922</v>
+        <v>121.9007186889648</v>
       </c>
       <c r="C182" t="n">
         <v>136.3000030517578</v>
@@ -5181,11 +5193,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>130.1287384033203</v>
+        <v>130.1287994384766</v>
       </c>
       <c r="C183" t="n">
         <v>145.5</v>
@@ -5210,11 +5222,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>135.2491912841797</v>
+        <v>135.2492523193359</v>
       </c>
       <c r="C184" t="n">
         <v>150.3999938964844</v>
@@ -5239,7 +5251,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
@@ -5268,11 +5280,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>143.6123809814453</v>
+        <v>143.6123962402344</v>
       </c>
       <c r="C186" t="n">
         <v>159.6999969482422</v>
@@ -5297,11 +5309,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>135.3849945068359</v>
+        <v>135.3849487304688</v>
       </c>
       <c r="C187" t="n">
         <v>149.7100067138672</v>
@@ -5326,11 +5338,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>134.6705780029297</v>
+        <v>134.6705627441406</v>
       </c>
       <c r="C188" t="n">
         <v>148.9199981689453</v>
@@ -5355,11 +5367,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>144.4281311035156</v>
+        <v>144.4281463623047</v>
       </c>
       <c r="C189" t="n">
         <v>159.7100067138672</v>
@@ -5384,11 +5396,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>138.2312469482422</v>
+        <v>138.2312316894531</v>
       </c>
       <c r="C190" t="n">
         <v>152.0099945068359</v>
@@ -5413,11 +5425,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>146.2972259521484</v>
+        <v>146.2971801757812</v>
       </c>
       <c r="C191" t="n">
         <v>160.8800048828125</v>
@@ -5442,11 +5454,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>133.6298828125</v>
+        <v>133.6298980712891</v>
       </c>
       <c r="C192" t="n">
         <v>146.9499969482422</v>
@@ -5471,11 +5483,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>143.0698089599609</v>
+        <v>143.0697937011719</v>
       </c>
       <c r="C193" t="n">
         <v>156.4299926757812</v>
@@ -5500,11 +5512,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>151.9870910644531</v>
+        <v>151.9870452880859</v>
       </c>
       <c r="C194" t="n">
         <v>166.1799926757812</v>
@@ -5529,11 +5541,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>157.1545715332031</v>
+        <v>157.1545867919922</v>
       </c>
       <c r="C195" t="n">
         <v>171.8300018310547</v>
@@ -5558,11 +5570,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>168.0012664794922</v>
+        <v>168.0012817382812</v>
       </c>
       <c r="C196" t="n">
         <v>182.7299957275391</v>
@@ -5587,11 +5599,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>157.2719421386719</v>
+        <v>157.2718963623047</v>
       </c>
       <c r="C197" t="n">
         <v>171.0599975585938</v>
@@ -5616,11 +5628,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>164.6087036132812</v>
+        <v>164.6086883544922</v>
       </c>
       <c r="C198" t="n">
         <v>179.0399932861328</v>
@@ -5645,11 +5657,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>156.3236236572266</v>
+        <v>156.3236694335938</v>
       </c>
       <c r="C199" t="n">
         <v>169.1300048828125</v>
@@ -5674,11 +5686,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>146.6834106445312</v>
+        <v>146.6833648681641</v>
       </c>
       <c r="C200" t="n">
         <v>158.6999969482422</v>
@@ -5703,11 +5715,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>149.4007873535156</v>
+        <v>149.4007568359375</v>
       </c>
       <c r="C201" t="n">
         <v>161.6399993896484</v>
@@ -5732,11 +5744,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>142.4072875976562</v>
+        <v>142.4073181152344</v>
       </c>
       <c r="C202" t="n">
         <v>153.1999969482422</v>
@@ -5761,11 +5773,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>171.465087890625</v>
+        <v>171.4651031494141</v>
       </c>
       <c r="C203" t="n">
         <v>184.4600067138672</v>
@@ -5790,7 +5802,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
@@ -5819,11 +5831,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>175.1478271484375</v>
+        <v>175.1478118896484</v>
       </c>
       <c r="C205" t="n">
         <v>187.4900054931641</v>
@@ -5848,7 +5860,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
@@ -5877,11 +5889,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>172.933837890625</v>
+        <v>172.9338226318359</v>
       </c>
       <c r="C207" t="n">
         <v>185.1199951171875</v>
@@ -5906,11 +5918,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>160.9684448242188</v>
+        <v>160.9684906005859</v>
       </c>
       <c r="C208" t="n">
         <v>171.4100036621094</v>
@@ -5935,11 +5947,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>170.1057434082031</v>
+        <v>170.1057739257812</v>
       </c>
       <c r="C209" t="n">
         <v>181.1399993896484</v>
@@ -5964,7 +5976,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
@@ -5993,11 +6005,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>164.0144500732422</v>
+        <v>164.0144805908203</v>
       </c>
       <c r="C211" t="n">
         <v>173.6600036621094</v>
@@ -6022,11 +6034,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>163.0227813720703</v>
+        <v>163.0227966308594</v>
       </c>
       <c r="C212" t="n">
         <v>172.6100006103516</v>
@@ -6051,11 +6063,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>152.2748107910156</v>
+        <v>152.2748260498047</v>
       </c>
       <c r="C213" t="n">
         <v>161.2299957275391</v>
@@ -6080,11 +6092,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>155.2056579589844</v>
+        <v>155.2056274414062</v>
       </c>
       <c r="C214" t="n">
         <v>163.3099975585938</v>
@@ -6109,7 +6121,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
@@ -6138,7 +6150,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
@@ -6167,11 +6179,11 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>182.0308685302734</v>
+        <v>182.0308532714844</v>
       </c>
       <c r="C217" t="n">
         <v>190.4900054931641</v>
@@ -6196,11 +6208,11 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>201.9740753173828</v>
+        <v>201.9740905761719</v>
       </c>
       <c r="C218" t="n">
         <v>211.3600006103516</v>
@@ -6225,11 +6237,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>211.1477508544922</v>
+        <v>211.1477661132812</v>
       </c>
       <c r="C219" t="n">
         <v>220.9600067138672</v>
@@ -6254,11 +6266,11 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>220.9214477539062</v>
+        <v>220.9214630126953</v>
       </c>
       <c r="C220" t="n">
         <v>230.1399993896484</v>
@@ -6283,11 +6295,11 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>203.6616668701172</v>
+        <v>203.6616821289062</v>
       </c>
       <c r="C221" t="n">
         <v>212.1600036621094</v>
@@ -6312,11 +6324,11 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>207.0598907470703</v>
+        <v>207.0599060058594</v>
       </c>
       <c r="C222" t="n">
         <v>215.6999969482422</v>
@@ -6341,11 +6353,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>196.1621856689453</v>
+        <v>196.1621704101562</v>
       </c>
       <c r="C223" t="n">
         <v>203.3399963378906</v>
@@ -6370,11 +6382,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>208.7997741699219</v>
+        <v>208.7997894287109</v>
       </c>
       <c r="C224" t="n">
         <v>216.4400024414062</v>
@@ -6399,7 +6411,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
@@ -6428,11 +6440,11 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>226.8435974121094</v>
+        <v>226.8435668945312</v>
       </c>
       <c r="C226" t="n">
         <v>234.1199951171875</v>
@@ -6457,7 +6469,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
@@ -6486,11 +6498,11 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>257.7715148925781</v>
+        <v>257.7715454101562</v>
       </c>
       <c r="C228" t="n">
         <v>266.0400085449219</v>
@@ -6515,7 +6527,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
@@ -6544,7 +6556,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
@@ -6573,7 +6585,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
@@ -6602,11 +6614,11 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>258.3657836914062</v>
+        <v>258.3657531738281</v>
       </c>
       <c r="C232" t="n">
         <v>264.4599914550781</v>
@@ -6631,7 +6643,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
@@ -6660,7 +6672,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
@@ -6689,7 +6701,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
@@ -6718,11 +6730,11 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>255.2917327880859</v>
+        <v>255.2917633056641</v>
       </c>
       <c r="C236" t="n">
         <v>260.239990234375</v>
@@ -6747,7 +6759,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
@@ -6776,11 +6788,11 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>275.0167846679688</v>
+        <v>275.0167541503906</v>
       </c>
       <c r="C238" t="n">
         <v>279.2200012207031</v>
@@ -6805,11 +6817,11 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>264.5763244628906</v>
+        <v>264.5763549804688</v>
       </c>
       <c r="C239" t="n">
         <v>268.6199951171875</v>
@@ -6834,7 +6846,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
@@ -6863,7 +6875,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6892,7 +6904,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6921,7 +6933,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -6950,7 +6962,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -6979,7 +6991,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -7008,11 +7020,11 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
-        <v>289.6843566894531</v>
+        <v>289.6843872070312</v>
       </c>
       <c r="C246" t="n">
         <v>291.8900146484375</v>
@@ -7037,7 +7049,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7066,7 +7078,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7095,7 +7107,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7124,32 +7136,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>360.3900146484375</v>
+        <v>362.3900146484375</v>
       </c>
       <c r="C250" t="n">
-        <v>360.3900146484375</v>
+        <v>362.3900146484375</v>
       </c>
       <c r="D250" t="n">
-        <v>24659100</v>
+        <v>25712600</v>
       </c>
       <c r="E250" t="n">
         <v>37.24</v>
       </c>
       <c r="F250" t="n">
-        <v>9.677497708067602</v>
+        <v>9.731203400871038</v>
       </c>
       <c r="G250" t="n">
         <v>208575022</v>
       </c>
       <c r="H250" t="n">
-        <v>75168355233.87817</v>
+        <v>75585505277.87817</v>
       </c>
       <c r="I250" t="n">
-        <v>0.118226524746573</v>
+        <v>0.1232774651223578</v>
       </c>
     </row>
   </sheetData>
@@ -7181,75 +7193,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39539</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39629</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40030</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7285,13 +7297,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39630</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39721</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40108</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7327,13 +7339,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40291</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7369,13 +7381,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40030</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7411,13 +7423,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40108</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7453,13 +7465,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40291</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7495,13 +7507,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40745</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7537,13 +7549,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40835</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7579,13 +7591,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40955</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7612,7 +7624,7 @@
       <c r="I10" t="n">
         <v>6.659999999999999</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40955</v>
       </c>
       <c r="K10" t="n">
@@ -7625,13 +7637,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40654</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7658,7 +7670,7 @@
       <c r="I11" t="n">
         <v>7.33</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40955</v>
       </c>
       <c r="K11" t="n">
@@ -7671,13 +7683,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40745</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7704,7 +7716,7 @@
       <c r="I12" t="n">
         <v>5.1</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40955</v>
       </c>
       <c r="K12" t="n">
@@ -7717,13 +7729,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40835</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7750,7 +7762,7 @@
       <c r="I13" t="n">
         <v>3.78</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40955</v>
       </c>
       <c r="K13" t="n">
@@ -7763,13 +7775,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40955</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7796,7 +7808,7 @@
       <c r="I14" t="n">
         <v>3.34</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40955</v>
       </c>
       <c r="K14" t="n">
@@ -7809,13 +7821,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>41018</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7842,7 +7854,7 @@
       <c r="I15" t="n">
         <v>3.44</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>41018</v>
       </c>
       <c r="K15" t="n">
@@ -7855,13 +7867,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41109</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7888,7 +7900,7 @@
       <c r="I16" t="n">
         <v>5.58</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41109</v>
       </c>
       <c r="K16" t="n">
@@ -7901,13 +7913,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41200</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7934,7 +7946,7 @@
       <c r="I17" t="n">
         <v>7</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41200</v>
       </c>
       <c r="K17" t="n">
@@ -7947,13 +7959,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41324</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -7980,7 +7992,7 @@
       <c r="I18" t="n">
         <v>6.27</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41324</v>
       </c>
       <c r="K18" t="n">
@@ -7993,13 +8005,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41387</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8026,7 +8038,7 @@
       <c r="I19" t="n">
         <v>6.58</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41387</v>
       </c>
       <c r="K19" t="n">
@@ -8039,13 +8051,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41478</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8072,7 +8084,7 @@
       <c r="I20" t="n">
         <v>7.73</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41478</v>
       </c>
       <c r="K20" t="n">
@@ -8085,13 +8097,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41569</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8118,7 +8130,7 @@
       <c r="I21" t="n">
         <v>7.82</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41569</v>
       </c>
       <c r="K21" t="n">
@@ -8131,13 +8143,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41683</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8164,7 +8176,7 @@
       <c r="I22" t="n">
         <v>9.74</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41683</v>
       </c>
       <c r="K22" t="n">
@@ -8177,13 +8189,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41751</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8210,7 +8222,7 @@
       <c r="I23" t="n">
         <v>10.36</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41751</v>
       </c>
       <c r="K23" t="n">
@@ -8223,13 +8235,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41842</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8256,7 +8268,7 @@
       <c r="I24" t="n">
         <v>9.9</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41842</v>
       </c>
       <c r="K24" t="n">
@@ -8269,13 +8281,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41933</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8302,7 +8314,7 @@
       <c r="I25" t="n">
         <v>10.29</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41933</v>
       </c>
       <c r="K25" t="n">
@@ -8315,13 +8327,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>42047</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8348,7 +8360,7 @@
       <c r="I26" t="n">
         <v>10.7</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>42047</v>
       </c>
       <c r="K26" t="n">
@@ -8361,13 +8373,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42115</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8394,7 +8406,7 @@
       <c r="I27" t="n">
         <v>10.3</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42115</v>
       </c>
       <c r="K27" t="n">
@@ -8407,13 +8419,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42206</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8440,7 +8452,7 @@
       <c r="I28" t="n">
         <v>10.88</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42206</v>
       </c>
       <c r="K28" t="n">
@@ -8453,13 +8465,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42297</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8486,7 +8498,7 @@
       <c r="I29" t="n">
         <v>11.16</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42297</v>
       </c>
       <c r="K29" t="n">
@@ -8499,13 +8511,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42411</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8532,7 +8544,7 @@
       <c r="I30" t="n">
         <v>10.88</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42411</v>
       </c>
       <c r="K30" t="n">
@@ -8545,13 +8557,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42481</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8578,7 +8590,7 @@
       <c r="I31" t="n">
         <v>10.63</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42481</v>
       </c>
       <c r="K31" t="n">
@@ -8591,13 +8603,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42572</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8624,7 +8636,7 @@
       <c r="I32" t="n">
         <v>10.34</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42572</v>
       </c>
       <c r="K32" t="n">
@@ -8637,13 +8649,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42663</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8670,7 +8682,7 @@
       <c r="I33" t="n">
         <v>9.82</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42663</v>
       </c>
       <c r="K33" t="n">
@@ -8683,13 +8695,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42782</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8716,7 +8728,7 @@
       <c r="I34" t="n">
         <v>10.27</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42782</v>
       </c>
       <c r="K34" t="n">
@@ -8729,13 +8741,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42845</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8762,7 +8774,7 @@
       <c r="I35" t="n">
         <v>10.14</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42845</v>
       </c>
       <c r="K35" t="n">
@@ -8775,13 +8787,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42936</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8808,7 +8820,7 @@
       <c r="I36" t="n">
         <v>10.01</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42936</v>
       </c>
       <c r="K36" t="n">
@@ -8821,13 +8833,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>43027</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8854,7 +8866,7 @@
       <c r="I37" t="n">
         <v>8.609999999999999</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>43027</v>
       </c>
       <c r="K37" t="n">
@@ -8867,13 +8879,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43146</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8900,7 +8912,7 @@
       <c r="I38" t="n">
         <v>7.31</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43146</v>
       </c>
       <c r="K38" t="n">
@@ -8913,13 +8925,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43214</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8946,7 +8958,7 @@
       <c r="I39" t="n">
         <v>7.56</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43214</v>
       </c>
       <c r="K39" t="n">
@@ -8959,13 +8971,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43300</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -8992,7 +9004,7 @@
       <c r="I40" t="n">
         <v>7.369999999999999</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43300</v>
       </c>
       <c r="K40" t="n">
@@ -9005,13 +9017,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43391</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9038,7 +9050,7 @@
       <c r="I41" t="n">
         <v>8.94</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43391</v>
       </c>
       <c r="K41" t="n">
@@ -9051,13 +9063,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43510</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9084,7 +9096,7 @@
       <c r="I42" t="n">
         <v>9.279999999999999</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43510</v>
       </c>
       <c r="K42" t="n">
@@ -9097,13 +9109,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43573</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9130,7 +9142,7 @@
       <c r="I43" t="n">
         <v>9.85</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43573</v>
       </c>
       <c r="K43" t="n">
@@ -9143,13 +9155,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43669</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9176,7 +9188,7 @@
       <c r="I44" t="n">
         <v>10.03</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43669</v>
       </c>
       <c r="K44" t="n">
@@ -9189,13 +9201,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43760</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9222,7 +9234,7 @@
       <c r="I45" t="n">
         <v>8.91</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43760</v>
       </c>
       <c r="K45" t="n">
@@ -9235,13 +9247,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43874</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9268,7 +9280,7 @@
       <c r="I46" t="n">
         <v>9.94</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43874</v>
       </c>
       <c r="K46" t="n">
@@ -9281,13 +9293,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43942</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9314,7 +9326,7 @@
       <c r="I47" t="n">
         <v>9.279999999999999</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43942</v>
       </c>
       <c r="K47" t="n">
@@ -9327,13 +9339,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>44035</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9360,7 +9372,7 @@
       <c r="I48" t="n">
         <v>7.02</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>44035</v>
       </c>
       <c r="K48" t="n">
@@ -9373,13 +9385,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44124</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9406,7 +9418,7 @@
       <c r="I49" t="n">
         <v>8.75</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44124</v>
       </c>
       <c r="K49" t="n">
@@ -9419,13 +9431,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44238</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9452,7 +9464,7 @@
       <c r="I50" t="n">
         <v>10.5</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44238</v>
       </c>
       <c r="K50" t="n">
@@ -9465,13 +9477,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44306</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9498,7 +9510,7 @@
       <c r="I51" t="n">
         <v>11.04</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44306</v>
       </c>
       <c r="K51" t="n">
@@ -9511,13 +9523,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44397</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9544,7 +9556,7 @@
       <c r="I52" t="n">
         <v>14.86</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44397</v>
       </c>
       <c r="K52" t="n">
@@ -9557,13 +9569,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44488</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9590,7 +9602,7 @@
       <c r="I53" t="n">
         <v>14.25</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44488</v>
       </c>
       <c r="K53" t="n">
@@ -9603,13 +9615,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44609</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9636,7 +9648,7 @@
       <c r="I54" t="n">
         <v>14.49</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44609</v>
       </c>
       <c r="K54" t="n">
@@ -9649,13 +9661,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44670</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9682,7 +9694,7 @@
       <c r="I55" t="n">
         <v>15.77</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44670</v>
       </c>
       <c r="K55" t="n">
@@ -9695,13 +9707,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44763</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9728,7 +9740,7 @@
       <c r="I56" t="n">
         <v>14.38</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44763</v>
       </c>
       <c r="K56" t="n">
@@ -9741,13 +9753,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44853</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9774,7 +9786,7 @@
       <c r="I57" t="n">
         <v>13.65</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44853</v>
       </c>
       <c r="K57" t="n">
@@ -9787,13 +9799,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44973</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9820,7 +9832,7 @@
       <c r="I58" t="n">
         <v>11.77</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44973</v>
       </c>
       <c r="K58" t="n">
@@ -9833,13 +9845,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>45035</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9866,7 +9878,7 @@
       <c r="I59" t="n">
         <v>11.75</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>45035</v>
       </c>
       <c r="K59" t="n">
@@ -9879,13 +9891,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45127</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9912,7 +9924,7 @@
       <c r="I60" t="n">
         <v>9.41</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45127</v>
       </c>
       <c r="K60" t="n">
@@ -9925,13 +9937,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45217</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -9958,7 +9970,7 @@
       <c r="I61" t="n">
         <v>9.259999999999998</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45217</v>
       </c>
       <c r="K61" t="n">
@@ -9971,13 +9983,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45337</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10004,7 +10016,7 @@
       <c r="I62" t="n">
         <v>12.79</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45337</v>
       </c>
       <c r="K62" t="n">
@@ -10017,13 +10029,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45399</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10050,7 +10062,7 @@
       <c r="I63" t="n">
         <v>13.46</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45399</v>
       </c>
       <c r="K63" t="n">
@@ -10063,13 +10075,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45492</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10096,7 +10108,7 @@
       <c r="I64" t="n">
         <v>15.82</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45492</v>
       </c>
       <c r="K64" t="n">
@@ -10109,13 +10121,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45582</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10142,7 +10154,7 @@
       <c r="I65" t="n">
         <v>19.5</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45582</v>
       </c>
       <c r="K65" t="n">
@@ -10155,13 +10167,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45701</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10188,7 +10200,7 @@
       <c r="I66" t="n">
         <v>21.47</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45701</v>
       </c>
       <c r="K66" t="n">
@@ -10201,13 +10213,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45763</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10234,7 +10246,7 @@
       <c r="I67" t="n">
         <v>18.37</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45763</v>
       </c>
       <c r="K67" t="n">
@@ -10247,13 +10259,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45855</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10280,7 +10292,7 @@
       <c r="I68" t="n">
         <v>22.61</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45855</v>
       </c>
       <c r="K68" t="n">
@@ -10293,13 +10305,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45946</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10326,7 +10338,7 @@
       <c r="I69" t="n">
         <v>25.43</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45946</v>
       </c>
       <c r="K69" t="n">
@@ -10339,13 +10351,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>46065</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10372,7 +10384,7 @@
       <c r="I70" t="n">
         <v>27.43</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>46065</v>
       </c>
       <c r="K70" t="n">
@@ -10385,13 +10397,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46128</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10418,7 +10430,7 @@
       <c r="I71" t="n">
         <v>33.51000000000001</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46128</v>
       </c>
       <c r="K71" t="n">
@@ -10431,13 +10443,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46220</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10464,7 +10476,7 @@
       <c r="I72" t="n">
         <v>37.24</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46220</v>
       </c>
       <c r="K72" t="n">
@@ -10501,52 +10513,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40021</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40030</v>
       </c>
       <c r="C2" t="n">
@@ -10575,10 +10587,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40102</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40108</v>
       </c>
       <c r="C3" t="n">
@@ -10607,10 +10619,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40220</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40227</v>
       </c>
       <c r="C4" t="n">
@@ -10639,10 +10651,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40288</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40291</v>
       </c>
       <c r="C5" t="n">
@@ -10671,10 +10683,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40375</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40381</v>
       </c>
       <c r="C6" t="n">
@@ -10703,10 +10715,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40466</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40472</v>
       </c>
       <c r="C7" t="n">
@@ -10735,10 +10747,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40584</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40591</v>
       </c>
       <c r="C8" t="n">
@@ -10767,10 +10779,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40648</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40654</v>
       </c>
       <c r="C9" t="n">
@@ -10799,10 +10811,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40739</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40745</v>
       </c>
       <c r="C10" t="n">
@@ -10831,10 +10843,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40830</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40835</v>
       </c>
       <c r="C11" t="n">
@@ -10863,10 +10875,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40949</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40955</v>
       </c>
       <c r="C12" t="n">
@@ -10895,10 +10907,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41012</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41018</v>
       </c>
       <c r="C13" t="n">
@@ -10927,10 +10939,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41106</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41109</v>
       </c>
       <c r="C14" t="n">
@@ -10959,10 +10971,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41197</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41200</v>
       </c>
       <c r="C15" t="n">
@@ -10991,10 +11003,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41316</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41324</v>
       </c>
       <c r="C16" t="n">
@@ -11023,10 +11035,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41382</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41387</v>
       </c>
       <c r="C17" t="n">
@@ -11055,10 +11067,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41474</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41478</v>
       </c>
       <c r="C18" t="n">
@@ -11087,10 +11099,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41565</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41569</v>
       </c>
       <c r="C19" t="n">
@@ -11119,10 +11131,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41677</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41683</v>
       </c>
       <c r="C20" t="n">
@@ -11151,10 +11163,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41747</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41751</v>
       </c>
       <c r="C21" t="n">
@@ -11183,10 +11195,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41838</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41842</v>
       </c>
       <c r="C22" t="n">
@@ -11215,10 +11227,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41929</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41933</v>
       </c>
       <c r="C23" t="n">
@@ -11247,10 +11259,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42041</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42047</v>
       </c>
       <c r="C24" t="n">
@@ -11279,10 +11291,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42111</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42115</v>
       </c>
       <c r="C25" t="n">
@@ -11311,10 +11323,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42202</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42206</v>
       </c>
       <c r="C26" t="n">
@@ -11343,10 +11355,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42293</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42297</v>
       </c>
       <c r="C27" t="n">
@@ -11375,10 +11387,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42405</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42411</v>
       </c>
       <c r="C28" t="n">
@@ -11407,10 +11419,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42478</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42481</v>
       </c>
       <c r="C29" t="n">
@@ -11439,10 +11451,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42569</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42572</v>
       </c>
       <c r="C30" t="n">
@@ -11471,10 +11483,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42660</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42663</v>
       </c>
       <c r="C31" t="n">
@@ -11503,10 +11515,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42776</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42782</v>
       </c>
       <c r="C32" t="n">
@@ -11535,10 +11547,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42842</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42845</v>
       </c>
       <c r="C33" t="n">
@@ -11567,10 +11579,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42933</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42936</v>
       </c>
       <c r="C34" t="n">
@@ -11599,10 +11611,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43024</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43027</v>
       </c>
       <c r="C35" t="n">
@@ -11631,10 +11643,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43140</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43146</v>
       </c>
       <c r="C36" t="n">
@@ -11663,10 +11675,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43209</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43214</v>
       </c>
       <c r="C37" t="n">
@@ -11695,10 +11707,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43297</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43300</v>
       </c>
       <c r="C38" t="n">
@@ -11727,10 +11739,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43388</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43391</v>
       </c>
       <c r="C39" t="n">
@@ -11759,10 +11771,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43504</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43510</v>
       </c>
       <c r="C40" t="n">
@@ -11791,10 +11803,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43570</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43573</v>
       </c>
       <c r="C41" t="n">
@@ -11823,10 +11835,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43665</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43669</v>
       </c>
       <c r="C42" t="n">
@@ -11855,10 +11867,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43756</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43760</v>
       </c>
       <c r="C43" t="n">
@@ -11887,10 +11899,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43868</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43874</v>
       </c>
       <c r="C44" t="n">
@@ -11919,10 +11931,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43938</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43942</v>
       </c>
       <c r="C45" t="n">
@@ -11951,10 +11963,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44032</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44035</v>
       </c>
       <c r="C46" t="n">
@@ -11983,10 +11995,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44120</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44124</v>
       </c>
       <c r="C47" t="n">
@@ -12015,10 +12027,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44232</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44238</v>
       </c>
       <c r="C48" t="n">
@@ -12047,10 +12059,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44301</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44306</v>
       </c>
       <c r="C49" t="n">
@@ -12079,10 +12091,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44392</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44397</v>
       </c>
       <c r="C50" t="n">
@@ -12111,10 +12123,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44483</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44488</v>
       </c>
       <c r="C51" t="n">
@@ -12143,10 +12155,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44606</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44609</v>
       </c>
       <c r="C52" t="n">
@@ -12175,10 +12187,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44665</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44670</v>
       </c>
       <c r="C53" t="n">
@@ -12207,10 +12219,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44760</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44763</v>
       </c>
       <c r="C54" t="n">
@@ -12239,10 +12251,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44848</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44853</v>
       </c>
       <c r="C55" t="n">
@@ -12271,10 +12283,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44970</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44973</v>
       </c>
       <c r="C56" t="n">
@@ -12303,10 +12315,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45030</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45035</v>
       </c>
       <c r="C57" t="n">
@@ -12335,10 +12347,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45124</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45127</v>
       </c>
       <c r="C58" t="n">
@@ -12367,10 +12379,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45212</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45217</v>
       </c>
       <c r="C59" t="n">
@@ -12399,10 +12411,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45334</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45337</v>
       </c>
       <c r="C60" t="n">
@@ -12431,10 +12443,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45393</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45399</v>
       </c>
       <c r="C61" t="n">
@@ -12463,10 +12475,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45488</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45492</v>
       </c>
       <c r="C62" t="n">
@@ -12495,10 +12507,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45579</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45582</v>
       </c>
       <c r="C63" t="n">
@@ -12527,10 +12539,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45695</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45701</v>
       </c>
       <c r="C64" t="n">
@@ -12559,10 +12571,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45758</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45763</v>
       </c>
       <c r="C65" t="n">
@@ -12591,10 +12603,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45849</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45855</v>
       </c>
       <c r="C66" t="n">
@@ -12623,10 +12635,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45940</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45946</v>
       </c>
       <c r="C67" t="n">
@@ -12655,10 +12667,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46058</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46065</v>
       </c>
       <c r="C68" t="n">
@@ -12687,10 +12699,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46121</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46128</v>
       </c>
       <c r="C69" t="n">
@@ -12719,10 +12731,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46213</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46220</v>
       </c>
       <c r="C70" t="n">
@@ -12769,12 +12781,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/TRV.xlsx
+++ b/salidas/empresas/TRV.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>28.01418304443359</v>
+        <v>28.01416397094727</v>
       </c>
       <c r="C2" t="n">
         <v>45.38000106811523</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>26.53258323669434</v>
+        <v>26.53259658813477</v>
       </c>
       <c r="C3" t="n">
         <v>42.97999954223633</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>25.93791007995605</v>
+        <v>25.93792343139648</v>
       </c>
       <c r="C4" t="n">
         <v>41.79000091552734</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>27.32822418212891</v>
+        <v>27.32822608947754</v>
       </c>
       <c r="C5" t="n">
         <v>44.02999877929688</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>27.32203483581543</v>
+        <v>27.32201957702637</v>
       </c>
       <c r="C6" t="n">
         <v>44.02000045776367</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>27.83898162841797</v>
+        <v>27.83899116516113</v>
       </c>
       <c r="C7" t="n">
         <v>44.58000183105469</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>28.60084533691406</v>
+        <v>28.6008472442627</v>
       </c>
       <c r="C8" t="n">
         <v>45.79999923706055</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>27.41435050964355</v>
+        <v>27.41434669494629</v>
       </c>
       <c r="C9" t="n">
         <v>43.90000152587891</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>29.45395469665527</v>
+        <v>29.45395851135254</v>
       </c>
       <c r="C10" t="n">
         <v>46.88999938964844</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>32.11731719970703</v>
+        <v>32.1173095703125</v>
       </c>
       <c r="C11" t="n">
         <v>51.13000106811523</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>32.54446029663086</v>
+        <v>32.54447174072266</v>
       </c>
       <c r="C12" t="n">
         <v>51.81000137329102</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>33.89519500732422</v>
+        <v>33.89517974853516</v>
       </c>
       <c r="C13" t="n">
         <v>53.68999862670898</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>32.03910827636719</v>
+        <v>32.03913879394531</v>
       </c>
       <c r="C15" t="n">
         <v>50.75</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>32.84823226928711</v>
+        <v>32.84823608398438</v>
       </c>
       <c r="C16" t="n">
         <v>51.77000045776367</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>34.32662963867188</v>
+        <v>34.32662582397461</v>
       </c>
       <c r="C17" t="n">
         <v>54.09999847412109</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>34.37104034423828</v>
+        <v>34.37102890014648</v>
       </c>
       <c r="C18" t="n">
         <v>54.16999816894531</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>34.12601852416992</v>
+        <v>34.12603378295898</v>
       </c>
       <c r="C19" t="n">
         <v>53.5</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>32.39100646972656</v>
+        <v>32.39102172851562</v>
       </c>
       <c r="C20" t="n">
         <v>50.77999877929688</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>32.23791885375977</v>
+        <v>32.2379264831543</v>
       </c>
       <c r="C21" t="n">
         <v>50.54000091552734</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>32.29548645019531</v>
+        <v>32.29547882080078</v>
       </c>
       <c r="C22" t="n">
         <v>50.34000015258789</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>33.49516677856445</v>
+        <v>33.49518203735352</v>
       </c>
       <c r="C23" t="n">
         <v>52.20999908447266</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>34.70099258422852</v>
+        <v>34.70100402832031</v>
       </c>
       <c r="C25" t="n">
         <v>53.79999923706055</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>31.02449798583984</v>
+        <v>31.02451324462891</v>
       </c>
       <c r="C26" t="n">
         <v>48.09999847412109</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>29.93445205688477</v>
+        <v>29.93445777893066</v>
       </c>
       <c r="C27" t="n">
         <v>46.40999984741211</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>31.05286598205566</v>
+        <v>31.05288696289062</v>
       </c>
       <c r="C28" t="n">
         <v>47.84999847412109</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>32.70774459838867</v>
+        <v>32.70775604248047</v>
       </c>
       <c r="C29" t="n">
         <v>50.40000152587891</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>32.32483673095703</v>
+        <v>32.32485580444336</v>
       </c>
       <c r="C30" t="n">
         <v>49.81000137329102</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>28.33419036865234</v>
+        <v>28.33420372009277</v>
       </c>
       <c r="C31" t="n">
         <v>43.40000152587891</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>28.80424308776855</v>
+        <v>28.80425453186035</v>
       </c>
       <c r="C32" t="n">
         <v>44.11999893188477</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>28.83035850524902</v>
+        <v>28.83035469055176</v>
       </c>
       <c r="C33" t="n">
         <v>44.15999984741211</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>29.71531867980957</v>
+        <v>29.71530342102051</v>
       </c>
       <c r="C34" t="n">
         <v>45.20000076293945</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>27.97315216064453</v>
+        <v>27.9731502532959</v>
       </c>
       <c r="C35" t="n">
         <v>42.54999923706055</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>28.69631958007812</v>
+        <v>28.69633865356445</v>
       </c>
       <c r="C36" t="n">
         <v>43.65000152587891</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>29.9221019744873</v>
+        <v>29.92209625244141</v>
       </c>
       <c r="C37" t="n">
         <v>45.20000076293945</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>25.57942581176758</v>
+        <v>25.57942008972168</v>
       </c>
       <c r="C38" t="n">
         <v>38.63999938964844</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>23.93106079101562</v>
+        <v>23.93106651306152</v>
       </c>
       <c r="C39" t="n">
         <v>36.15000152587891</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>27.14333915710449</v>
+        <v>27.14332389831543</v>
       </c>
       <c r="C40" t="n">
         <v>40.63999938964844</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>27.47729110717773</v>
+        <v>27.4772891998291</v>
       </c>
       <c r="C41" t="n">
         <v>41.13999938964844</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>27.15669441223145</v>
+        <v>27.15668296813965</v>
       </c>
       <c r="C42" t="n">
         <v>40.65999984741211</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>27.59975051879883</v>
+        <v>27.5997486114502</v>
       </c>
       <c r="C43" t="n">
         <v>41.04000091552734</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>28.96494293212891</v>
+        <v>28.96495246887207</v>
       </c>
       <c r="C44" t="n">
         <v>43.06999969482422</v>
@@ -1315,7 +1315,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>33.90787124633789</v>
+        <v>33.90786743164062</v>
       </c>
       <c r="C45" t="n">
         <v>50.41999816894531</v>
@@ -1340,7 +1340,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>33.30697250366211</v>
+        <v>33.30694580078125</v>
       </c>
       <c r="C46" t="n">
         <v>49.22999954223633</v>
@@ -1365,7 +1365,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>33.68583297729492</v>
+        <v>33.68582153320312</v>
       </c>
       <c r="C47" t="n">
         <v>49.79000091552734</v>
@@ -1390,7 +1390,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>35.44487762451172</v>
+        <v>35.44488906860352</v>
       </c>
       <c r="C48" t="n">
         <v>52.38999938964844</v>
@@ -1415,7 +1415,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>33.95478057861328</v>
+        <v>33.95476913452148</v>
       </c>
       <c r="C49" t="n">
         <v>49.86000061035156</v>
@@ -1440,7 +1440,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>34.50638198852539</v>
+        <v>34.50638580322266</v>
       </c>
       <c r="C50" t="n">
         <v>50.66999816894531</v>
@@ -1465,7 +1465,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>35.81390762329102</v>
+        <v>35.81390380859375</v>
       </c>
       <c r="C51" t="n">
         <v>52.59000015258789</v>
@@ -1490,7 +1490,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>36.95937347412109</v>
+        <v>36.9593620300293</v>
       </c>
       <c r="C52" t="n">
         <v>53.93999862670898</v>
@@ -1540,7 +1540,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>33.89656066894531</v>
+        <v>33.89654922485352</v>
       </c>
       <c r="C54" t="n">
         <v>49.47000122070312</v>
@@ -1565,7 +1565,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>33.99937057495117</v>
+        <v>33.99936676025391</v>
       </c>
       <c r="C55" t="n">
         <v>49.25</v>
@@ -1590,7 +1590,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>34.82778549194336</v>
+        <v>34.82778930664062</v>
       </c>
       <c r="C56" t="n">
         <v>50.45000076293945</v>
@@ -1615,7 +1615,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>33.81989288330078</v>
+        <v>33.81988525390625</v>
       </c>
       <c r="C57" t="n">
         <v>48.9900016784668</v>
@@ -1665,7 +1665,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>38.38254928588867</v>
+        <v>38.3825569152832</v>
       </c>
       <c r="C59" t="n">
         <v>55.20000076293945</v>
@@ -1690,7 +1690,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>37.54120254516602</v>
+        <v>37.54117965698242</v>
       </c>
       <c r="C60" t="n">
         <v>53.9900016784668</v>
@@ -1715,7 +1715,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>38.99314117431641</v>
+        <v>38.99314498901367</v>
       </c>
       <c r="C61" t="n">
         <v>55.70999908447266</v>
@@ -1765,7 +1765,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>41.94685745239258</v>
+        <v>41.94686889648438</v>
       </c>
       <c r="C63" t="n">
         <v>59.93000030517578</v>
@@ -1790,7 +1790,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>41.88763427734375</v>
+        <v>41.88764953613281</v>
       </c>
       <c r="C64" t="n">
         <v>59.47999954223633</v>
@@ -1815,7 +1815,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>44.56371307373047</v>
+        <v>44.563720703125</v>
       </c>
       <c r="C65" t="n">
         <v>63.27999877929688</v>
@@ -1890,7 +1890,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>39.08597183227539</v>
+        <v>39.08594512939453</v>
       </c>
       <c r="C68" t="n">
         <v>55.13000106811523</v>
@@ -1915,7 +1915,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>35.7750244140625</v>
+        <v>35.77502059936523</v>
       </c>
       <c r="C69" t="n">
         <v>50.45999908447266</v>
@@ -1940,7 +1940,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>34.8428840637207</v>
+        <v>34.84287261962891</v>
       </c>
       <c r="C70" t="n">
         <v>48.72999954223633</v>
@@ -1965,7 +1965,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>41.72135162353516</v>
+        <v>41.72134780883789</v>
       </c>
       <c r="C71" t="n">
         <v>58.34999847412109</v>
@@ -1990,7 +1990,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>40.21981048583984</v>
+        <v>40.21982192993164</v>
       </c>
       <c r="C72" t="n">
         <v>56.25</v>
@@ -2015,7 +2015,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>42.62339019775391</v>
+        <v>42.62338256835938</v>
       </c>
       <c r="C73" t="n">
         <v>59.16999816894531</v>
@@ -2040,7 +2040,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>41.99668884277344</v>
+        <v>41.99667739868164</v>
       </c>
       <c r="C74" t="n">
         <v>58.29999923706055</v>
@@ -2065,7 +2065,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>41.75896835327148</v>
+        <v>41.75897979736328</v>
       </c>
       <c r="C75" t="n">
         <v>57.97000122070312</v>
@@ -2094,7 +2094,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>42.95402908325195</v>
+        <v>42.95403289794922</v>
       </c>
       <c r="C76" t="n">
         <v>59.20000076293945</v>
@@ -2123,7 +2123,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>46.66896820068359</v>
+        <v>46.66896438598633</v>
       </c>
       <c r="C77" t="n">
         <v>64.31999969482422</v>
@@ -2152,7 +2152,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>45.34116744995117</v>
+        <v>45.34117889404297</v>
       </c>
       <c r="C78" t="n">
         <v>62.4900016784668</v>
@@ -2181,7 +2181,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>46.67381286621094</v>
+        <v>46.6738166809082</v>
       </c>
       <c r="C79" t="n">
         <v>63.84000015258789</v>
@@ -2239,7 +2239,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>47.3317985534668</v>
+        <v>47.33181762695312</v>
       </c>
       <c r="C81" t="n">
         <v>64.73999786376953</v>
@@ -2268,7 +2268,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>50.26361846923828</v>
+        <v>50.26362228393555</v>
       </c>
       <c r="C82" t="n">
         <v>68.26000213623047</v>
@@ -2297,7 +2297,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>52.23704147338867</v>
+        <v>52.23703002929688</v>
       </c>
       <c r="C83" t="n">
         <v>70.94000244140625</v>
@@ -2326,7 +2326,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>52.14866638183594</v>
+        <v>52.14867782592773</v>
       </c>
       <c r="C84" t="n">
         <v>70.81999969482422</v>
@@ -2355,7 +2355,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>53.21582794189453</v>
+        <v>53.2158317565918</v>
       </c>
       <c r="C85" t="n">
         <v>71.81999969482422</v>
@@ -2384,7 +2384,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>58.13579940795898</v>
+        <v>58.13582611083984</v>
       </c>
       <c r="C86" t="n">
         <v>78.45999908447266</v>
@@ -2442,7 +2442,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>62.73580551147461</v>
+        <v>62.73578262329102</v>
       </c>
       <c r="C88" t="n">
         <v>84.19000244140625</v>
@@ -2471,7 +2471,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>63.64491271972656</v>
+        <v>63.6449089050293</v>
       </c>
       <c r="C89" t="n">
         <v>85.41000366210938</v>
@@ -2500,7 +2500,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>62.38554763793945</v>
+        <v>62.38557052612305</v>
       </c>
       <c r="C90" t="n">
         <v>83.72000122070312</v>
@@ -2529,7 +2529,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>59.9182014465332</v>
+        <v>59.91820526123047</v>
       </c>
       <c r="C91" t="n">
         <v>79.91999816894531</v>
@@ -2558,7 +2558,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>62.63972473144531</v>
+        <v>62.63970565795898</v>
       </c>
       <c r="C92" t="n">
         <v>83.55000305175781</v>
@@ -2587,7 +2587,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>59.9031982421875</v>
+        <v>59.90322113037109</v>
       </c>
       <c r="C93" t="n">
         <v>79.90000152587891</v>
@@ -2616,7 +2616,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>63.9508171081543</v>
+        <v>63.95080947875977</v>
       </c>
       <c r="C94" t="n">
         <v>84.76999664306641</v>
@@ -2645,7 +2645,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>65.10506439208984</v>
+        <v>65.10504913330078</v>
       </c>
       <c r="C95" t="n">
         <v>86.30000305175781</v>
@@ -2674,7 +2674,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>68.45461273193359</v>
+        <v>68.45460510253906</v>
       </c>
       <c r="C96" t="n">
         <v>90.73999786376953</v>
@@ -2703,7 +2703,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>68.69440460205078</v>
+        <v>68.69439697265625</v>
       </c>
       <c r="C97" t="n">
         <v>90.54000091552734</v>
@@ -2732,7 +2732,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>61.66865158081055</v>
+        <v>61.66864776611328</v>
       </c>
       <c r="C98" t="n">
         <v>81.27999877929688</v>
@@ -2761,7 +2761,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>63.6109733581543</v>
+        <v>63.61097717285156</v>
       </c>
       <c r="C99" t="n">
         <v>83.83999633789062</v>
@@ -2790,7 +2790,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>64.95188903808594</v>
+        <v>64.951904296875</v>
       </c>
       <c r="C100" t="n">
         <v>85.09999847412109</v>
@@ -2848,7 +2848,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>71.32496643066406</v>
+        <v>71.32493591308594</v>
       </c>
       <c r="C102" t="n">
         <v>93.44999694824219</v>
@@ -2877,7 +2877,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>72.21638488769531</v>
+        <v>72.21639251708984</v>
       </c>
       <c r="C103" t="n">
         <v>94.06999969482422</v>
@@ -2935,7 +2935,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>72.70769500732422</v>
+        <v>72.70771789550781</v>
       </c>
       <c r="C105" t="n">
         <v>94.70999908447266</v>
@@ -2993,7 +2993,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>77.83732604980469</v>
+        <v>77.83734893798828</v>
       </c>
       <c r="C107" t="n">
         <v>100.8000030517578</v>
@@ -3022,7 +3022,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>80.65584564208984</v>
+        <v>80.65586090087891</v>
       </c>
       <c r="C108" t="n">
         <v>104.4499969482422</v>
@@ -3051,7 +3051,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>82.16650390625</v>
+        <v>82.16651916503906</v>
       </c>
       <c r="C109" t="n">
         <v>105.8499984741211</v>
@@ -3080,7 +3080,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>79.81447601318359</v>
+        <v>79.81446075439453</v>
       </c>
       <c r="C110" t="n">
         <v>102.8199996948242</v>
@@ -3109,7 +3109,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>83.4007568359375</v>
+        <v>83.40076446533203</v>
       </c>
       <c r="C111" t="n">
         <v>107.4400024414062</v>
@@ -3138,7 +3138,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>84.36759948730469</v>
+        <v>84.36762237548828</v>
       </c>
       <c r="C112" t="n">
         <v>108.129997253418</v>
@@ -3167,7 +3167,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>78.89031982421875</v>
+        <v>78.89034271240234</v>
       </c>
       <c r="C113" t="n">
         <v>101.1100006103516</v>
@@ -3196,7 +3196,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>78.89813232421875</v>
+        <v>78.89810180664062</v>
       </c>
       <c r="C114" t="n">
         <v>101.120002746582</v>
@@ -3225,7 +3225,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>75.88433837890625</v>
+        <v>75.88435363769531</v>
       </c>
       <c r="C115" t="n">
         <v>96.66000366210938</v>
@@ -3254,7 +3254,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>83.31108093261719</v>
+        <v>83.31105041503906</v>
       </c>
       <c r="C116" t="n">
         <v>106.120002746582</v>
@@ -3283,7 +3283,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>78.15320587158203</v>
+        <v>78.15317535400391</v>
       </c>
       <c r="C117" t="n">
         <v>99.55000305175781</v>
@@ -3312,7 +3312,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>78.62808227539062</v>
+        <v>78.62810516357422</v>
       </c>
       <c r="C118" t="n">
         <v>99.52999877929688</v>
@@ -3370,7 +3370,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>90.50960540771484</v>
+        <v>90.50959777832031</v>
       </c>
       <c r="C120" t="n">
         <v>114.5699996948242</v>
@@ -3399,7 +3399,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>89.64008331298828</v>
+        <v>89.64011383056641</v>
       </c>
       <c r="C121" t="n">
         <v>112.8600006103516</v>
@@ -3428,7 +3428,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>85.01752471923828</v>
+        <v>85.01754760742188</v>
       </c>
       <c r="C122" t="n">
         <v>107.0400009155273</v>
@@ -3544,7 +3544,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>91.16039276123047</v>
+        <v>91.16041564941406</v>
       </c>
       <c r="C126" t="n">
         <v>114.1399993896484</v>
@@ -3573,7 +3573,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>95.63310241699219</v>
+        <v>95.63311004638672</v>
       </c>
       <c r="C127" t="n">
         <v>119.0400009155273</v>
@@ -3602,7 +3602,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>93.36763000488281</v>
+        <v>93.36760711669922</v>
       </c>
       <c r="C128" t="n">
         <v>116.2200012207031</v>
@@ -3631,7 +3631,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>95.36798858642578</v>
+        <v>95.36800384521484</v>
       </c>
       <c r="C129" t="n">
         <v>118.7099990844727</v>
@@ -3660,7 +3660,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>92.54576110839844</v>
+        <v>92.54578399658203</v>
       </c>
       <c r="C130" t="n">
         <v>114.5500030517578</v>
@@ -3689,7 +3689,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>87.39940643310547</v>
+        <v>87.39942169189453</v>
       </c>
       <c r="C131" t="n">
         <v>108.1800003051758</v>
@@ -3718,7 +3718,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>91.57627105712891</v>
+        <v>91.57628631591797</v>
       </c>
       <c r="C132" t="n">
         <v>113.3499984741211</v>
@@ -3747,7 +3747,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>99.47446441650391</v>
+        <v>99.4744873046875</v>
       </c>
       <c r="C133" t="n">
         <v>122.4199981689453</v>
@@ -3776,7 +3776,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>95.70415496826172</v>
+        <v>95.70416259765625</v>
       </c>
       <c r="C134" t="n">
         <v>117.7799987792969</v>
@@ -3834,7 +3834,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>98.48709106445312</v>
+        <v>98.48711395263672</v>
       </c>
       <c r="C136" t="n">
         <v>120.5400009155273</v>
@@ -3863,7 +3863,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>99.40219879150391</v>
+        <v>99.40219116210938</v>
       </c>
       <c r="C137" t="n">
         <v>121.6600036621094</v>
@@ -3892,7 +3892,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>102.0085830688477</v>
+        <v>102.0085678100586</v>
       </c>
       <c r="C138" t="n">
         <v>124.8499984741211</v>
@@ -3921,7 +3921,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>103.9848403930664</v>
+        <v>103.9848251342773</v>
       </c>
       <c r="C139" t="n">
         <v>126.5299987792969</v>
@@ -3979,7 +3979,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>99.588134765625</v>
+        <v>99.58812713623047</v>
       </c>
       <c r="C141" t="n">
         <v>121.1800003051758</v>
@@ -4008,7 +4008,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>101.3089447021484</v>
+        <v>101.3089370727539</v>
       </c>
       <c r="C142" t="n">
         <v>122.5199966430664</v>
@@ -4037,7 +4037,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>109.5197982788086</v>
+        <v>109.5198287963867</v>
       </c>
       <c r="C143" t="n">
         <v>132.4499969482422</v>
@@ -4066,7 +4066,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>112.0996704101562</v>
+        <v>112.0996856689453</v>
       </c>
       <c r="C144" t="n">
         <v>135.5700073242188</v>
@@ -4124,7 +4124,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>124.634033203125</v>
+        <v>124.6339721679688</v>
       </c>
       <c r="C146" t="n">
         <v>149.9199981689453</v>
@@ -4153,7 +4153,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>115.555778503418</v>
+        <v>115.555793762207</v>
       </c>
       <c r="C147" t="n">
         <v>139</v>
@@ -4211,7 +4211,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>109.9740447998047</v>
+        <v>109.9740524291992</v>
       </c>
       <c r="C149" t="n">
         <v>131.6000061035156</v>
@@ -4240,7 +4240,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>107.4001922607422</v>
+        <v>107.4001846313477</v>
       </c>
       <c r="C150" t="n">
         <v>128.5200042724609</v>
@@ -4269,7 +4269,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>102.8507385253906</v>
+        <v>102.8507690429688</v>
       </c>
       <c r="C151" t="n">
         <v>122.3399963378906</v>
@@ -4298,7 +4298,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>109.4081954956055</v>
+        <v>109.4081649780273</v>
       </c>
       <c r="C152" t="n">
         <v>130.1399993896484</v>
@@ -4327,7 +4327,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>110.6355972290039</v>
+        <v>110.635627746582</v>
       </c>
       <c r="C153" t="n">
         <v>131.6000061035156</v>
@@ -4356,7 +4356,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>109.6837539672852</v>
+        <v>109.6837692260742</v>
       </c>
       <c r="C154" t="n">
         <v>129.7100067138672</v>
@@ -4385,7 +4385,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>105.8108673095703</v>
+        <v>105.8108901977539</v>
       </c>
       <c r="C155" t="n">
         <v>125.129997253418</v>
@@ -4414,7 +4414,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>110.2418594360352</v>
+        <v>110.2418518066406</v>
       </c>
       <c r="C156" t="n">
         <v>130.3699951171875</v>
@@ -4443,7 +4443,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>101.8870697021484</v>
+        <v>101.8870849609375</v>
       </c>
       <c r="C157" t="n">
         <v>119.75</v>
@@ -4530,7 +4530,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>117.3874816894531</v>
+        <v>117.3874664306641</v>
       </c>
       <c r="C160" t="n">
         <v>137.1600036621094</v>
@@ -4559,7 +4559,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>123.0274887084961</v>
+        <v>123.0275115966797</v>
       </c>
       <c r="C161" t="n">
         <v>143.75</v>
@@ -4588,7 +4588,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>124.5851440429688</v>
+        <v>124.5851516723633</v>
       </c>
       <c r="C162" t="n">
         <v>145.5700073242188</v>
@@ -4617,7 +4617,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>128.6738739013672</v>
+        <v>128.6738891601562</v>
       </c>
       <c r="C163" t="n">
         <v>149.5200042724609</v>
@@ -4646,7 +4646,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>126.1781845092773</v>
+        <v>126.1781616210938</v>
       </c>
       <c r="C164" t="n">
         <v>146.6199951171875</v>
@@ -4675,7 +4675,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>126.4707717895508</v>
+        <v>126.4707489013672</v>
       </c>
       <c r="C165" t="n">
         <v>146.9600067138672</v>
@@ -4704,7 +4704,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>128.6497802734375</v>
+        <v>128.6497650146484</v>
       </c>
       <c r="C166" t="n">
         <v>148.6900024414062</v>
@@ -4733,7 +4733,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>113.3959274291992</v>
+        <v>113.3959121704102</v>
       </c>
       <c r="C167" t="n">
         <v>131.0599975585938</v>
@@ -4762,7 +4762,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>118.293098449707</v>
+        <v>118.2930755615234</v>
       </c>
       <c r="C168" t="n">
         <v>136.7200012207031</v>
@@ -4791,7 +4791,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>119.2123641967773</v>
+        <v>119.2123184204102</v>
       </c>
       <c r="C169" t="n">
         <v>136.9499969482422</v>
@@ -4820,7 +4820,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>114.5726776123047</v>
+        <v>114.5726623535156</v>
       </c>
       <c r="C170" t="n">
         <v>131.6199951171875</v>
@@ -4849,7 +4849,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>104.2922821044922</v>
+        <v>104.2923049926758</v>
       </c>
       <c r="C171" t="n">
         <v>119.8099975585938</v>
@@ -4878,7 +4878,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>87.05406188964844</v>
+        <v>87.05408477783203</v>
       </c>
       <c r="C172" t="n">
         <v>99.34999847412109</v>
@@ -4965,7 +4965,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>100.6027984619141</v>
+        <v>100.6028137207031</v>
       </c>
       <c r="C175" t="n">
         <v>114.0500030517578</v>
@@ -4994,7 +4994,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>100.9291839599609</v>
+        <v>100.9291763305664</v>
       </c>
       <c r="C176" t="n">
         <v>114.4199981689453</v>
@@ -5023,7 +5023,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>102.3581695556641</v>
+        <v>102.3581771850586</v>
       </c>
       <c r="C177" t="n">
         <v>116.0400009155273</v>
@@ -5110,7 +5110,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>115.2245712280273</v>
+        <v>115.2245483398438</v>
       </c>
       <c r="C180" t="n">
         <v>129.6499938964844</v>
@@ -5139,7 +5139,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>125.5407180786133</v>
+        <v>125.5407562255859</v>
       </c>
       <c r="C181" t="n">
         <v>140.3699951171875</v>
@@ -5168,7 +5168,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>121.9007186889648</v>
+        <v>121.9007110595703</v>
       </c>
       <c r="C182" t="n">
         <v>136.3000030517578</v>
@@ -5197,7 +5197,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>130.1287994384766</v>
+        <v>130.1287536621094</v>
       </c>
       <c r="C183" t="n">
         <v>145.5</v>
@@ -5226,7 +5226,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>135.2492523193359</v>
+        <v>135.2492218017578</v>
       </c>
       <c r="C184" t="n">
         <v>150.3999938964844</v>
@@ -5284,7 +5284,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>143.6123962402344</v>
+        <v>143.6123809814453</v>
       </c>
       <c r="C186" t="n">
         <v>159.6999969482422</v>
@@ -5313,7 +5313,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>135.3849487304688</v>
+        <v>135.3849639892578</v>
       </c>
       <c r="C187" t="n">
         <v>149.7100067138672</v>
@@ -5371,7 +5371,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>144.4281463623047</v>
+        <v>144.4281616210938</v>
       </c>
       <c r="C189" t="n">
         <v>159.7100067138672</v>
@@ -5400,7 +5400,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>138.2312316894531</v>
+        <v>138.231201171875</v>
       </c>
       <c r="C190" t="n">
         <v>152.0099945068359</v>
@@ -5429,7 +5429,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>146.2971801757812</v>
+        <v>146.2971954345703</v>
       </c>
       <c r="C191" t="n">
         <v>160.8800048828125</v>
@@ -5516,7 +5516,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>151.9870452880859</v>
+        <v>151.987060546875</v>
       </c>
       <c r="C194" t="n">
         <v>166.1799926757812</v>
@@ -5545,7 +5545,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>157.1545867919922</v>
+        <v>157.154541015625</v>
       </c>
       <c r="C195" t="n">
         <v>171.8300018310547</v>
@@ -5574,7 +5574,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>168.0012817382812</v>
+        <v>168.0012359619141</v>
       </c>
       <c r="C196" t="n">
         <v>182.7299957275391</v>
@@ -5632,7 +5632,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>164.6086883544922</v>
+        <v>164.6086730957031</v>
       </c>
       <c r="C198" t="n">
         <v>179.0399932861328</v>
@@ -5661,7 +5661,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>156.3236694335938</v>
+        <v>156.3236541748047</v>
       </c>
       <c r="C199" t="n">
         <v>169.1300048828125</v>
@@ -5690,7 +5690,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>146.6833648681641</v>
+        <v>146.6833953857422</v>
       </c>
       <c r="C200" t="n">
         <v>158.6999969482422</v>
@@ -5719,7 +5719,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>149.4007568359375</v>
+        <v>149.4007873535156</v>
       </c>
       <c r="C201" t="n">
         <v>161.6399993896484</v>
@@ -5777,7 +5777,7 @@
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>171.4651031494141</v>
+        <v>171.465087890625</v>
       </c>
       <c r="C203" t="n">
         <v>184.4600067138672</v>
@@ -5806,7 +5806,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>176.4381866455078</v>
+        <v>176.4381713867188</v>
       </c>
       <c r="C204" t="n">
         <v>189.8099975585938</v>
@@ -5835,7 +5835,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>175.1478118896484</v>
+        <v>175.1477966308594</v>
       </c>
       <c r="C205" t="n">
         <v>187.4900054931641</v>
@@ -5864,7 +5864,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>178.5388488769531</v>
+        <v>178.5388793945312</v>
       </c>
       <c r="C206" t="n">
         <v>191.1199951171875</v>
@@ -5922,7 +5922,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>160.9684906005859</v>
+        <v>160.9684753417969</v>
       </c>
       <c r="C208" t="n">
         <v>171.4100036621094</v>
@@ -5951,7 +5951,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>170.1057739257812</v>
+        <v>170.1057434082031</v>
       </c>
       <c r="C209" t="n">
         <v>181.1399993896484</v>
@@ -6038,7 +6038,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>163.0227966308594</v>
+        <v>163.0227508544922</v>
       </c>
       <c r="C212" t="n">
         <v>172.6100006103516</v>
@@ -6096,7 +6096,7 @@
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>155.2056274414062</v>
+        <v>155.2056732177734</v>
       </c>
       <c r="C214" t="n">
         <v>163.3099975585938</v>
@@ -6154,7 +6154,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>171.6566467285156</v>
+        <v>171.6566314697266</v>
       </c>
       <c r="C216" t="n">
         <v>180.6199951171875</v>
@@ -6212,7 +6212,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>201.9740905761719</v>
+        <v>201.9740600585938</v>
       </c>
       <c r="C218" t="n">
         <v>211.3600006103516</v>
@@ -6270,7 +6270,7 @@
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>220.9214630126953</v>
+        <v>220.9214782714844</v>
       </c>
       <c r="C220" t="n">
         <v>230.1399993896484</v>
@@ -6328,7 +6328,7 @@
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>207.0599060058594</v>
+        <v>207.0598602294922</v>
       </c>
       <c r="C222" t="n">
         <v>215.6999969482422</v>
@@ -6357,7 +6357,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>196.1621704101562</v>
+        <v>196.1622161865234</v>
       </c>
       <c r="C223" t="n">
         <v>203.3399963378906</v>
@@ -6415,7 +6415,7 @@
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>220.0192413330078</v>
+        <v>220.0192565917969</v>
       </c>
       <c r="C225" t="n">
         <v>228.0700073242188</v>
@@ -6444,7 +6444,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>226.8435668945312</v>
+        <v>226.8435821533203</v>
       </c>
       <c r="C226" t="n">
         <v>234.1199951171875</v>
@@ -6502,7 +6502,7 @@
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>257.7715454101562</v>
+        <v>257.7715148925781</v>
       </c>
       <c r="C228" t="n">
         <v>266.0400085449219</v>
@@ -6589,7 +6589,7 @@
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>251.5044250488281</v>
+        <v>251.5044555664062</v>
       </c>
       <c r="C231" t="n">
         <v>258.489990234375</v>
@@ -6618,7 +6618,7 @@
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>258.3657531738281</v>
+        <v>258.3657836914062</v>
       </c>
       <c r="C232" t="n">
         <v>264.4599914550781</v>
@@ -6647,7 +6647,7 @@
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>258.0434265136719</v>
+        <v>258.04345703125</v>
       </c>
       <c r="C233" t="n">
         <v>264.1300048828125</v>
@@ -6705,7 +6705,7 @@
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>262.4529724121094</v>
+        <v>262.4530029296875</v>
       </c>
       <c r="C235" t="n">
         <v>267.5400085449219</v>
@@ -6734,7 +6734,7 @@
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>255.2917633056641</v>
+        <v>255.2917022705078</v>
       </c>
       <c r="C236" t="n">
         <v>260.239990234375</v>
@@ -6763,7 +6763,7 @@
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>266.3474731445312</v>
+        <v>266.3475036621094</v>
       </c>
       <c r="C237" t="n">
         <v>271.510009765625</v>
@@ -6792,7 +6792,7 @@
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>275.0167541503906</v>
+        <v>275.0167846679688</v>
       </c>
       <c r="C238" t="n">
         <v>279.2200012207031</v>
